--- a/results/result_evaluation_logs/I_Advance_Adaption_Baseline.xlsx
+++ b/results/result_evaluation_logs/I_Advance_Adaption_Baseline.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X51"/>
+  <dimension ref="A1:W51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,11 +544,6 @@
           <t>Result String</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Langfuse Trace ID</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -625,11 +620,6 @@
 </t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>e2ef1ace-128a-44f8-831f-2b63c15b627f</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -705,11 +695,6 @@
 &lt;http://www.wikidata.org/entity/Q20992419&gt; &lt;http://www.wikidata.org/entity/P5072&gt; &lt;http://www.wikidata.org/entity/Q120&gt; .
 &lt;http://www.wikidata.org/entity/Q20992419&gt; &lt;http://www.wikidata.org/entity/P136&gt; &lt;http://www.wikidata.org/entity/Q20992419&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>348bdd53-cdb5-495f-ac19-61844d532b3d</t>
         </is>
       </c>
     </row>
@@ -790,11 +775,6 @@
 </t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0242cd05-d23d-4d30-88c8-1e8e1d69d92e</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -840,10 +820,10 @@
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
         <v>5</v>
@@ -877,11 +857,6 @@
 </t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>393d5531-ea01-4d9c-b724-4891b1eb135d</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -955,11 +930,6 @@
           <t xml:space="preserve">
 &lt;http://www.wikidata.org/entity/Q36771&gt; &lt;http://www.wikidata.org/entity/P27&gt; &lt;http://www.wikidata.org/entity/Q29999&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2474f905-6750-44d4-b0a1-8792cc786983</t>
         </is>
       </c>
     </row>
@@ -1039,11 +1009,6 @@
 </t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>ca8d55f8-4e31-4847-b117-a58f4e8127c1</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1119,11 +1084,6 @@
 &lt;http://www.wikidata.org/entity/Q2226643&gt; &lt;http://www.wikidata.org/entity/P31&gt; &lt;http://www.wikidata.org/entity/Q65943&gt; .
 &lt;http://www.wikidata.org/entity/Q2226643&gt; &lt;http://www.wikidata.org/entity/P101&gt; &lt;http://www.wikidata.org/entity/Q395&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>42bed9e5-44e9-43bd-9652-14d8f9810daf</t>
         </is>
       </c>
     </row>
@@ -1207,11 +1167,6 @@
 </t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>918353dd-d5fe-400a-af26-7b6de44bb781</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1257,10 +1212,10 @@
         <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q10" t="n">
         <v>7</v>
@@ -1293,11 +1248,6 @@
 </t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>3c90b558-4904-4cda-b2b0-bb2adc6c6f49</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1343,10 +1293,10 @@
         <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q11" t="n">
         <v>6</v>
@@ -1378,11 +1328,6 @@
 </t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>b8d3c5e7-2fd9-475f-8073-89e73ba490dd</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1461,11 +1406,6 @@
 </t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>731ec069-ee53-4102-86d3-4fe23fe34727</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1540,11 +1480,6 @@
 &lt;http://www.wikidata.org/entity/Q516760&gt; &lt;http://www.wikidata.org/entity/P276&gt; &lt;http://www.wikidata.org/entity/Q1605654&gt; .
 &lt;http://www.wikidata.org/entity/Q516760&gt; &lt;http://www.wikidata.org/entity/P710&gt; &lt;http://www.wikidata.org/entity/Q271108&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>f92b15cc-f4a2-400e-babf-66ad2fdd31a5</t>
         </is>
       </c>
     </row>
@@ -1624,11 +1559,6 @@
 &lt;http://www.wikidata.org/entity/Q7992209&gt; &lt;http://www.wikidata.org/entity/P200&gt; &lt;http://www.wikidata.org/entity/Q3561541&gt; .
 &lt;http://www.wikidata.org/entity/Q3561541&gt; &lt;http://www.wikidata.org/entity/P200&gt; &lt;http://www.wikidata.org/entity/Q5364109&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>f4fe021e-034f-471b-8945-a6981a6099b7</t>
         </is>
       </c>
     </row>
@@ -1711,11 +1641,6 @@
 </t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>15344e60-9579-4e70-a0a6-c781b99efb26</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1789,11 +1714,6 @@
           <t xml:space="preserve">
 &lt;http://www.wikidata.org/entity/Q3311362&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q66117&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>5794a8b3-a3b3-4d9c-902c-4cf4b326dc39</t>
         </is>
       </c>
     </row>
@@ -1874,11 +1794,6 @@
 </t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>eb3a57ab-4adc-44d9-96a6-e53ecc677bac</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1954,11 +1869,6 @@
 &lt;http://www.wikidata.org/entity/Q607380&gt; &lt;http://www.wikidata.org/entity/P183&gt; &lt;http://www.wikidata.org/entity/Q664&gt; .
 &lt;http://www.wikidata.org/entity/Q607380&gt; &lt;http://www.wikidata.org/entity/P1672&gt; &lt;http://www.wikidata.org/entity/Q782&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>137bf6d4-ecc6-4b3d-a24d-e70de54351a2</t>
         </is>
       </c>
     </row>
@@ -2042,11 +1952,6 @@
 </t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>eacae726-79c5-47d9-a89c-dafcfb2a4941</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2122,11 +2027,6 @@
 </t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>f1245038-78fd-4a81-be50-ef7fcf021094</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2172,10 +2072,10 @@
         <v>6</v>
       </c>
       <c r="O21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q21" t="n">
         <v>7</v>
@@ -2210,11 +2110,6 @@
 </t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>55fa0648-85b1-46db-8854-cb985bb9f237</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2290,11 +2185,6 @@
 </t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>83d22ba5-90e4-4734-a45b-d09781825c93</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2372,11 +2262,6 @@
 </t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>f1995c20-48d3-446b-b461-e74a88bd8534</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2451,11 +2336,6 @@
 &lt;http://www.wikidata.org/entity/Q188197&gt; &lt;http://www.wikidata.org/entity/P2522&gt; &lt;http://www.wikidata.org/entity/Q1856183&gt; .
 &lt;http://www.wikidata.org/entity/Q188197&gt; &lt;http://www.wikidata.org/entity/P2522&gt; &lt;http://www.wikidata.org/entity/Q674962&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>a79e4268-906e-44a1-a57f-b84d1344a2b8</t>
         </is>
       </c>
     </row>
@@ -2536,11 +2416,6 @@
 &lt;http://www.wikidata.org/entity/Q520445&gt; &lt;http://www.wikidata.org/entity/P176&gt; &lt;http://www.wikidata.org/entity/Q220072&gt; .
 &lt;http://www.wikidata.org/entity/Q220072&gt; &lt;http://www.wikidata.org/entity/P162&gt; &lt;http://www.wikidata.org/entity/Q5554167&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>eb408c36-fc3e-44af-9fbf-589fb3a5eee4</t>
         </is>
       </c>
     </row>
@@ -2626,11 +2501,6 @@
 </t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>8c9950e4-f83c-441a-87e5-ab48d0159962</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2709,11 +2579,6 @@
 </t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>8da03d18-8761-4334-9b19-f375e6cefffb</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2788,11 +2653,6 @@
 &lt;http://www.wikidata.org/entity/Q22082365&gt; &lt;http://www.wikidata.org/entity/P276&gt; &lt;http://www.wikidata.org/entity/Q965&gt; .
 &lt;http://www.wikidata.org/entity/Q965&gt; &lt;http://www.wikidata.org/entity/P463&gt; &lt;http://www.wikidata.org/entity/Q47543&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>f3559215-3750-4364-9dc7-61ed2447d96a</t>
         </is>
       </c>
     </row>
@@ -2876,11 +2736,6 @@
 </t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>0ff8fe5a-5511-42b2-9c9d-988a626ff85f</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2959,11 +2814,6 @@
 </t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>f853f782-dc5e-4667-bfa3-d52062008606</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3009,10 +2859,10 @@
         <v>3</v>
       </c>
       <c r="O31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
         <v>4</v>
@@ -3044,11 +2894,6 @@
 </t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>a633fc20-e664-429c-88d1-f77e7f49e79e</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3094,10 +2939,10 @@
         <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
         <v>3</v>
@@ -3126,11 +2971,6 @@
 </t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>6a1116de-9c03-4f8d-903d-f84be4ce8661</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3176,10 +3016,10 @@
         <v>3</v>
       </c>
       <c r="O33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
         <v>5</v>
@@ -3212,11 +3052,6 @@
 </t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>2e9d8091-1107-4f4b-8a47-be2e8a98649a</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3294,11 +3129,6 @@
 </t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>f3dd5ddc-c263-4568-bd24-b7d1c3fa9d97</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3375,11 +3205,6 @@
 </t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>9da59610-f316-46c6-9634-9bcf8ce671af</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3456,11 +3281,6 @@
 </t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>c1212e84-c058-4965-b9d6-248ad0e1f66e</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3536,11 +3356,6 @@
 &lt;http://www.wikidata.org/entity/Q2616869&gt; &lt;http://www.wikidata.org/entity/P1433&gt; &lt;http://www.wikidata.org/entity/Q1126800&gt; .
 &lt;http://www.wikidata.org/entity/Q2616869&gt; &lt;http://www.wikidata.org/entity/P6216&gt; &lt;http://www.wikidata.org/entity/Q19652&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>9e9d1eb8-4e04-4fea-98e7-cf313e6ab517</t>
         </is>
       </c>
     </row>
@@ -3621,11 +3436,6 @@
 </t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>98f27496-f05c-449b-8064-a7a56251541d</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3702,11 +3512,6 @@
 </t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>05382497-81d9-49e8-8c13-d3bfef8d14b0</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3782,11 +3587,6 @@
 </t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>a4d547b6-cecc-4cb6-980e-cc57a235b3fc</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3863,11 +3663,6 @@
 </t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>9060f8e4-5520-4645-90c9-c1d557078f0e</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3907,7 +3702,7 @@
         <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
         <v>4</v>
@@ -3950,11 +3745,6 @@
 </t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>a89e7e93-b4c7-4c0e-a276-06df591f4bd4</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4029,11 +3819,6 @@
 &lt;http://www.wikidata.org/entity/Q87412161&gt; &lt;http://www.wikidata.org/entity/P3373&gt; &lt;http://www.wikidata.org/entity/Q95994024&gt; .
 &lt;http://www.wikidata.org/entity/Q87412161&gt; &lt;http://www.wikidata.org/entity/P31&gt; &lt;http://www.wikidata.org/entity/Q5&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>862642a5-baa5-4058-8c7e-a2cf87ac3655</t>
         </is>
       </c>
     </row>
@@ -4114,11 +3899,6 @@
 </t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>d65a0743-9c9d-46d6-8d36-2795710ec334</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4164,10 +3944,10 @@
         <v>4</v>
       </c>
       <c r="O45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q45" t="n">
         <v>7</v>
@@ -4201,11 +3981,6 @@
 </t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>6582b78d-fd23-4c11-b1cc-52ad3e7e485d</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4283,11 +4058,6 @@
 </t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>8f78ba0c-884d-49ad-b5b8-9d65c4cee4b4</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4365,11 +4135,6 @@
 </t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>298f675f-9262-4abf-a45c-f658f9a3408c</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4445,11 +4210,6 @@
 &lt;http://www.wikidata.org/entity/Q977911&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q112686&gt; .
 &lt;http://www.wikidata.org/entity/Q979352&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q112686&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>9f980691-474a-463a-896f-c0f470534ef2</t>
         </is>
       </c>
     </row>
@@ -4531,11 +4291,6 @@
 </t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>34a47558-d3e3-4b84-9278-18687c4424a5</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4575,16 +4330,16 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N50" t="n">
         <v>2</v>
       </c>
       <c r="O50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q50" t="n">
         <v>5</v>
@@ -4615,11 +4370,6 @@
 </t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>1acc0b2d-be0b-4e8b-957b-e2a6455d434a</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4693,11 +4443,6 @@
           <t xml:space="preserve">
 &lt;http://www.wikidata.org/entity/Q2362697&gt; &lt;http://www.wikidata.org/entity/P556&gt; &lt;http://www.wikidata.org/entity/Q503601&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>3ba93238-941b-466f-9799-c31f4bc6c47a</t>
         </is>
       </c>
     </row>
